--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260909.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260909.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>10,100,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>15.86%</t>
+          <t>15.59%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.62%</t>
+          <t>6.46%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.95%</t>
+          <t>6.09%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>5.44%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.13%</t>
+          <t>5.31%</t>
         </is>
       </c>
     </row>
@@ -726,51 +726,51 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.79%</t>
+          <t>4.92%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>1,115,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>4.06%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>1,115,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>3.91%</t>
         </is>
       </c>
     </row>
@@ -792,161 +792,161 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>1,987,956</t>
+          <t>2,307,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>1,987,956</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,307,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>210,500</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>600,000</t>
+          <t>580,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>580,000</t>
+          <t>13,500,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>13,500,000</t>
+          <t>2,640,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -968,68 +968,68 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2,640,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>140,500</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,900,000</t>
+          <t>1,293,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,44 +1041,44 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,293,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>1,900,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -1122,51 +1122,51 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>5,360,000</t>
+          <t>760,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>650,000</t>
+          <t>5,360,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,22 +1283,22 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
@@ -1481,88 +1481,88 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>400,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>191,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>191,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>7,235,460,895</t>
+          <t>6,895,086,642</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,888,873,681</t>
+          <t>3,152,903,551</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>3,854,421,740</t>
+          <t>4,074,325,080</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
